--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -11632,7 +11632,7 @@
           <t>A | 1696呎 (4+房)
 $8686万
 $51,217/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -11655,7 +11655,7 @@
           <t>A | 1696呎 (4+房)
 $8217万
 $48,447/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11701,7 +11701,7 @@
           <t>A | 1696呎 (4+房)
 $7975万
 $47,021/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11724,7 +11724,7 @@
           <t>A | 1696呎 (4+房)
 $7836万
 $46,200/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -11732,7 +11732,7 @@
           <t>B | 1594呎 (4+房)
 $6927万
 $43,459/呎
-(26年-04月-10日)</t>
+(26年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
           <t>A | 1696呎 (4+房)
 $7800万
 $45,991/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11770,7 +11770,7 @@
           <t>A | 1696呎 (4+房)
 $8293万
 $48,895/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11862,7 +11862,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -11870,7 +11870,7 @@
           <t>B | 1594呎 (4+房)
 $6927万
 $43,457/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -11885,7 +11885,7 @@
           <t>A | 1696呎 (4+房)
 $7552万
 $44,530/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -11893,7 +11893,7 @@
           <t>B | 1594呎 (4+房)
 $6942万
 $43,549/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12008,7 @@
           <t>B | 1594呎 (4+房)
 $6331万
 $39,720/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
           <t>A | 1696呎 (4+房)
 $5851万
 $34,500/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -12123,7 +12123,7 @@
           <t>B | 1594呎 (4+房)
 $5420万
 $34,000/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
           <t>A | 1696呎 (4+房)
 $5902万
 $34,800/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -12603,7 +12603,7 @@
           <t>B | 922呎 (3房)
 $3704万
 $40,168/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -12634,7 +12634,7 @@
           <t>B | 922呎 (3房)
 $3942万
 $42,757/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -12719,7 +12719,7 @@
           <t>A | 918呎 (3房)
 $3715万
 $40,463/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -12781,7 +12781,7 @@
           <t>A | 918呎 (3房)
 $3710万
 $40,410/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -12812,7 +12812,7 @@
           <t>A | 918呎 (3房)
 $3612万
 $39,350/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -12905,7 +12905,7 @@
           <t>A | 918呎 (3房)
 $3534万
 $38,500/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12936,7 +12936,7 @@
           <t>A | 918呎 (3房)
 $3689万
 $40,184/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12967,7 +12967,7 @@
           <t>A | 918呎 (3房)
 $3488万
 $38,000/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -12975,7 +12975,7 @@
           <t>B | 922呎 (3房)
 $3630万
 $39,376/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -13006,7 +13006,7 @@
           <t>B | 922呎 (3房)
 $3411万
 $37,000/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -13122,7 +13122,7 @@
           <t>A | 918呎 (3房)
 $3479万
 $37,898/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -13130,7 +13130,7 @@
           <t>B | 922呎 (3房)
 $3135万
 $34,000/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -13153,7 +13153,7 @@
           <t>A | 918呎 (3房)
 $3011万
 $32,800/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -13161,7 +13161,7 @@
           <t>B | 922呎 (3房)
 $3239万
 $35,130/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -13192,7 +13192,7 @@
           <t>B | 922呎 (3房)
 $3024万
 $32,800/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -10938,23 +10938,19 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>30478000</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>33200</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -10963,12 +10959,12 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M150" s="3" t="inlineStr">
@@ -10978,7 +10974,7 @@
       </c>
       <c r="N150" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12286,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -12300,7 +12296,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13210,12 +13206,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
+$3048万
+$33,200/呎
+(26年-08月-04日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -13211,7 +13211,7 @@
           <t>A | 918呎 (3房)
 $3048万
 $33,200/呎
-(26年-08月-04日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
